--- a/www/download/COUNTRY.WWW.EXI382.xlsx
+++ b/www/download/COUNTRY.WWW.EXI382.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>Mundo</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -967,2643 +972,4879 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.20020046325279</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.20020876424189</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2001909603105</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.20019063478152</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.20019065982221</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.20019573056216</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.20018707900338</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.20018015525229</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.20015273569551</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.20016684612495</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2001696882434</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.20016017278077</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.20015855765619</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.20015860773757</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.20018184549894</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.20017414548642</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.20018670339301</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.20016971328409</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.20017513459371</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2001813947665</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.20018781770377</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.20020220358082</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.20019740828847</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.20018398647803</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.20018048078127</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.20018333542006</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2001847752598</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>5030.831</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2421.185</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2460.121</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2481.973</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>2525.223</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>2569.599</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2602.571</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2643.028</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>2683.428</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>2709.457</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2765.362</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2796.728</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2862.592</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2945.443</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>2944.472</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>2965.027</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>3024.664</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>3042.368</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>3104.553</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>3114.106</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>3152.194</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>3546.102</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>3531.887</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>3730.031</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>3746.113</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>4065.732</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>4221.8</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2397.238</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>1010.923</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>1199.235</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>1210.63</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>1198.223</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>1249.011</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1262.331</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>1282.979</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>1307.228</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>1325.152</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>1365.398</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>1380.875</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>1433.558</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>1491.668</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>1485.384</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>1516.619</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>1576.852</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>1549.631</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>1594.722</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>1617.766</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>1623.331</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>1793.077</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>1768.501</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>1846.456</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>1870.706</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>2023.138</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>2086.421</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>11000657.389</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>5232651.458</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>5333773.702</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>5386235.29</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>5459557.684</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>5554913.631</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5631652.78</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>5709485.457</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>5783239.12</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>5840760.727</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>5963892.532</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>6091927.764</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>6206653.288</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>6339773.926</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>6312404.542</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>6321974.889</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>6493726.574</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>6537703.842</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>6647957.989</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>6678508.4</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>6782760.549</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>7654694.296</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>7630963.816</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>8072181.981</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>8128137.498</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>8827988.904</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>9176606.758</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>5009868.646</t>
+          <t>14580490333687.3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-238287.253</t>
+          <t>7528535139649.73</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-260091.912</t>
+          <t>7765442412425.85</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-271245.199</t>
+          <t>7594667062322.59</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-292851.937</t>
+          <t>7913259608642.71</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-309693.079</t>
+          <t>8077057200130.58</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-344900.639</t>
+          <t>8238449907915.58</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-356106.299</t>
+          <t>8316580970540.14</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>-320702.298</t>
+          <t>8461906784812.99</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-303323.388</t>
+          <t>8929574204109.28</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>-237536.435</t>
+          <t>9164721088433.29</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>-245126.246</t>
+          <t>9297294932392.37</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>-114754.022</t>
+          <t>9335300930547.86</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>14445.24</t>
+          <t>9606875951564.09</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>-11089.385</t>
+          <t>9376417874810.78</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>87505.678</t>
+          <t>9551482957694.52</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>237549.724</t>
+          <t>9884202800823.79</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>75934.396</t>
+          <t>9909469035212.8</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>123918.924</t>
+          <t>10082223252975.4</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>3413000.044</t>
+          <t>10022552679791.3</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>3411071.673</t>
+          <t>10090980019682.5</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>3741968.382</t>
+          <t>11201623910197.5</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>3688627.404</t>
+          <t>11079240120318.1</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>3850459.319</t>
+          <t>11723937928643.6</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>3910300.898</t>
+          <t>11785433690304.9</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>4227335.057</t>
+          <t>12785995754338.5</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>4354920.835</t>
+          <t>13412376849767.6</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>3942265851125.94</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1923119401310.57</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2158366396444.42</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2574595771798.4</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2383338313076.63</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2515592308216.03</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2604129615408.61</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2704214604894.07</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2712560346978.97</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2550483201493.98</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2543823511569.3</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2720457513015.52</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2662341080867.92</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2689565053212.09</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>2753883845354.51</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>2631878313908.4</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>2662872194102.29</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>2651761855494.7</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>2609761821122.46</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2521191671184.88</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>2438626954321.08</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>2895576728283.87</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2771061029902.25</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>3055715519350.91</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2844315885970.86</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>3346456310896.45</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>3486283475625.89</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>19286691579283.2</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>21303347066604.5</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>23026160767.6195</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>4464631426.8718</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>4973797625.91927</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>17556602773.4903</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>337011496903.692</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>1845477251.30151</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>33987831212.1455</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2025473627.52797</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>25009416219.9205</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2645107417.38288</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>161105284994.992</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>54313408054.9366</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>11968206663.6603</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1260596440.43779</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>56505930384.0673</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1105838478.78276</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>776363999.064357</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>36058117345859.2</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>3427991302318225</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>8360187339234.57</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>-1949465785401533</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>3018096900045.83</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2830107480276.86</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>3072019336139.58</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>3142586218067.49</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>30008346.0539386</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>30757208.3180457</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>34008664.0809212</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>35318238.1016596</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>37707194.583684</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>45758027.2756815</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>46312272.2155776</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>45416275.2873675</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>42163862.7084468</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>41523239.2596369</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>45198436.9467397</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>48941284.8196848</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>51469613.0898277</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>52274214.492323</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>51867519.2523628</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>60145823.0731874</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>63759417.9476912</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>70533697.7544693</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>70411069.3724331</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>73421536.4305263</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>83777475.7984412</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>85950787.5027791</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>90719519.9608979</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>93257290.3648926</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>100428968.218163</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>103857617.145691</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>106132211.630627</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>54350274.2827501</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>57209883.8151937</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>64271647.1876827</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>64622574.1065296</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>71023838.1844459</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>86657240.0827002</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>88750773.4552537</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>86847033.7418469</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>81173223.2938115</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>83709594.98089</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>92103355.3348949</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>99948801.7679264</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>103975761.651795</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>107515443.752738</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>105157924.510046</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>123532765.103892</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>133083978.216761</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>147268078.882938</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>146363425.745529</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>150601270.332599</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>171285779.629825</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>173305227.25441</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>181224134.969356</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>186509735.397727</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>199761577.622657</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>206167238.989671</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>212326779.862302</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0.270809436796882</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>-1.1239066345221</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>-1.12050405923172</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-1.10535447997368</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-1.12287468171552</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-1.12310940756109</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-1.1324437296949</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-1.13168566504705</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>-1.11822863151893</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-1.11892781249414</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>-1.09337771812301</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>-1.09010478745804</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>-1.04310267476552</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>-0.994629153861289</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>-1.00402681657355</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>-0.966751624796704</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>-0.91079191671667</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>-0.971364549199299</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>-0.95251715176329</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0.3537249400049</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>0.398767313227183</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>0.292305033834779</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>0.331124563689267</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>0.26008435491021</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>0.374777294400602</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>0.263227326014448</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>0.249158556913149</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1644.50353323573</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1902.34024525877</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1799.78541221515</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2126.65707190105</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1989.06009406303</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2014.06683648425</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2062.95245674462</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2107.76154702166</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2075.04684925404</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>1924.67195583727</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>1863.06352006141</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>1970.09710941416</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>1857.15666216709</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>1803.0584763475</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1853.98838631029</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>1735.35935974364</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>1688.72670419131</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1711.22126609944</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>1636.49974527583</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>1558.44041197273</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>1502.23674317724</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>1614.86501928981</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>1566.89827109396</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>1654.90857900435</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>1520.45052818713</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>1654.09156013678</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>1670.93975165446</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>13.061</t>
+          <t>-2.74181365966797e-05</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>13.623</t>
+          <t>9.23871994018555e-07</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>15.042</t>
+          <t>-1.69873237609863e-05</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>15.458</t>
+          <t>-1.48415565490723e-05</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>16.975</t>
+          <t>9.77516174316406e-06</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>-1.60336494445801e-05</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>20.793</t>
+          <t>4.69088554382324e-05</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>20.319</t>
+          <t>-1.71661376953125e-05</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>18.742</t>
+          <t>7.62939453125e-06</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>18.866</t>
+          <t>3.87430191040039e-06</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>20.117</t>
+          <t>1.16527080535889e-05</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>21.722</t>
+          <t>2.16662883758545e-05</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>22.117</t>
+          <t>5.36441802978516e-07</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>22.528</t>
+          <t>-1.12950801849365e-05</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>23.107</t>
+          <t>-2.19643115997314e-05</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>25.969</t>
+          <t>-3.22461128234863e-05</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>27.335</t>
+          <t>2.4259090423584e-05</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>30.455</t>
+          <t>7.15255737304688e-06</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>29.889</t>
+          <t>1.07288360595703e-05</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>30.539</t>
+          <t>-7.09295272827148e-06</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>35.036</t>
+          <t>-1.51395797729492e-05</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>35.58</t>
+          <t>9.5367431640625e-07</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>37.279</t>
+          <t>2.19345092773438e-05</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>37.58</t>
+          <t>2.41994857788086e-05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>39.987</t>
+          <t>2.53915786743164e-05</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>41.162</t>
+          <t>1.82390213012695e-05</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>42.998</t>
+          <t>-2.288818359375e-05</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>8.47578048706055e-05</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1.76429748535156e-05</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>-1.0758638381958e-05</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>6.28829002380371e-06</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1.49011611938477e-06</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-3.33786010742188e-05</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>-1.26957893371582e-05</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>6.19888305664062e-06</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>-1.63912773132324e-05</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2.49147415161133e-05</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>-3.05771827697754e-05</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>-1.99079513549805e-05</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>-2.15470790863037e-05</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>1.26361846923828e-05</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>-3.09944152832031e-06</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>3.91006469726562e-05</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>8.70227813720703e-06</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>3.22461128234863e-05</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>-3.00407409667969e-05</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>-3.51667404174805e-06</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>-3.06367874145508e-05</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>-4.66108322143555e-05</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>-1.02519989013672e-05</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>4.65512275695801e-05</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>8.16583633422852e-06</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>-2.02655792236328e-06</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>4.40478324890137e-05</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>8.56071710586548e-06</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>-2.46241688728333e-06</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>-1.56275928020477e-06</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-2.32085585594177e-06</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-6.66826963424683e-07</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>4.29153442382812e-06</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-3.3155083656311e-06</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-2.67662107944489e-06</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>1.52364373207092e-06</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>1.53668224811554e-06</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>1.26659870147705e-07</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>3.44216823577881e-06</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>1.54227018356323e-06</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>-2.3283064365387e-06</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>9.68575477600098e-07</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>7.69272446632385e-07</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>4.56720590591431e-06</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>-5.00679016113281e-06</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>4.24683094024658e-07</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>9.94652509689331e-07</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>-1.92224979400635e-06</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>2.83122062683105e-06</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>-1.53854489326477e-06</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>4.76837158203125e-07</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>1.97999179363251e-06</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>-8.94069671630859e-08</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>1.82539224624634e-07</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>43.349</t>
+          <t>2089.85060888179</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>45.677</t>
+          <t>-235.712577505968</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>51.181</t>
+          <t>-216.881447917961</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>51.473</t>
+          <t>-224.052849892475</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>56.414</t>
+          <t>-244.405125971046</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>68.559</t>
+          <t>-247.950575028017</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>70.325</t>
+          <t>-273.225117554519</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>68.945</t>
+          <t>-277.561981080153</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>64.708</t>
+          <t>-245.329949324981</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>66.874</t>
+          <t>-228.897025476539</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>73.555</t>
+          <t>-173.968620221563</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>79.902</t>
+          <t>-177.51518131547</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>83.248</t>
+          <t>-80.0484195980139</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>86.083</t>
+          <t>9.68394965556145</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>83.853</t>
+          <t>-7.46567116116492</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>98.291</t>
+          <t>57.6978791053079</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>105.781</t>
+          <t>150.648072470282</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>116.846</t>
+          <t>49.0015923745046</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>116.108</t>
+          <t>77.7056690443468</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>119.319</t>
+          <t>2109.69965319899</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>135.06</t>
+          <t>2101.27965308518</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>136.589</t>
+          <t>2086.89819339192</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>142.874</t>
+          <t>2085.73677745541</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>146.798</t>
+          <t>2085.32440921006</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>157.028</t>
+          <t>2090.28086341107</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>161.948</t>
+          <t>2089.49365849466</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>166.699</t>
+          <t>2087.2686888655</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>13.061</t>
+          <t>2186.64833206031</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>13.623</t>
+          <t>2161.19479695028</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>15.042</t>
+          <t>2168.09411852154</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>15.458</t>
+          <t>2170.14299995517</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>16.975</t>
+          <t>2162.01039001734</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>2161.78196407038</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>20.793</t>
+          <t>2163.88018406478</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>20.319</t>
+          <t>2160.20610176527</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>18.742</t>
+          <t>2155.16827588574</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>18.866</t>
+          <t>2155.69416027992</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>20.117</t>
+          <t>2156.64067259728</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>21.722</t>
+          <t>2178.23366761024</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>22.117</t>
+          <t>2168.19350486294</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>22.528</t>
+          <t>2152.40106553724</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>23.107</t>
+          <t>2143.81538436717</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>25.969</t>
+          <t>2132.18088297846</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>27.335</t>
+          <t>2146.92492056608</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>30.455</t>
+          <t>2148.88643024957</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>29.889</t>
+          <t>2141.35788117097</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>30.539</t>
+          <t>2144.5989765263</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>35.036</t>
+          <t>2151.75872731255</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>35.58</t>
+          <t>2158.62231890127</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>37.279</t>
+          <t>2160.5910530346</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>37.58</t>
+          <t>2164.10563346252</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>39.987</t>
+          <t>2169.75246198487</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>41.162</t>
+          <t>2171.31621293572</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>42.998</t>
+          <t>2173.62409449134</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>5401739.7501367</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>5949835.82494346</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>6986787.66527631</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>6941905.49981414</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>7664886.58695783</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>9917973.35005809</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>9866113.02675482</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>9778447.9620063</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>9202996.62310472</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>10062067.037453</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>11451669.7076924</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>13026964.5263179</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>13336491.5179116</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>14344044.5149765</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>12361400.7522201</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>15799878.1717562</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>17868562.790414</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>19996587.713094</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>19753917.6538862</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>19920059.0480388</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>21624559.2119724</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>21328785.0731429</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>22991970.4618798</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>24100250.8812803</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>25019155.8535687</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>25971251.8006735</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>27052923.7655711</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2286717444045.65</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>942997830270.497</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1032389876324.95</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>1027713263204.67</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1109022230619.86</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>1242523904373.51</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1291549603346.06</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>1321963511455.86</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>1255010078043.14</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>1496516732429.32</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>1560854650223.92</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>1589494353719.71</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>1350874424779.69</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>1626873481625.24</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>1466099638040.56</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>1599486848099.59</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>1723777544092.76</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1828282859481.93</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>1894054727301.95</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>1773384238699.17</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>1714052583580.17</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>1841131926910.61</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>1886700029759.19</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>2052334392068.97</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>1952908636675.52</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>2154201162782.44</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>2213336766491.64</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>5401739.7501367</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>5949835.82494346</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>6986787.66527631</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>6941905.49981414</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>7664886.58695783</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>9917973.35005809</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>9866113.02675482</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>9778447.9620063</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>9202996.62310472</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>10062067.037453</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>11451669.7076924</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>13026964.5263179</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>13336491.5179116</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>14344044.5149765</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>12361400.7522201</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>15799878.1717562</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>17868562.790414</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>19996587.713094</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>19753917.6538862</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>19920059.0480388</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>21624559.2119724</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>21328785.0731429</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>22991970.4618798</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>24100250.8812803</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>25019155.8535687</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>25971251.8006735</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>27052923.7655711</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>11000657.389</t>
+          <t>2286717444045.65</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>5232651.458</t>
+          <t>942997830270.497</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>5333773.702</t>
+          <t>1032389876324.95</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>5386235.29</t>
+          <t>1027713263204.67</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>5459557.684</t>
+          <t>1109022230619.86</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>5554913.631</t>
+          <t>1242523904373.51</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>5631652.78</t>
+          <t>1291549603346.06</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>5709485.457</t>
+          <t>1321963511455.86</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>5783239.12</t>
+          <t>1255010078043.14</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>5840760.727</t>
+          <t>1496516732429.32</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>5963892.532</t>
+          <t>1560854650223.92</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>6091927.764</t>
+          <t>1589494353719.71</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>6206653.288</t>
+          <t>1350874424779.69</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>6339773.926</t>
+          <t>1626873481625.24</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>6312404.542</t>
+          <t>1466099638040.56</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>6321974.889</t>
+          <t>1599486848099.59</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>6493726.574</t>
+          <t>1723777544092.76</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>6537703.842</t>
+          <t>1828282859481.93</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>6647957.989</t>
+          <t>1894054727301.95</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>6678508.4</t>
+          <t>1773384238699.17</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>6782760.549</t>
+          <t>1714052583580.17</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>7654694.296</t>
+          <t>1841131926910.61</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>7630963.816</t>
+          <t>1886700029759.19</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>8072181.981</t>
+          <t>2052334392068.97</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>8128137.498</t>
+          <t>1952908636675.52</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>8827988.904</t>
+          <t>2154201162782.44</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>9176606.758</t>
+          <t>2213336766491.64</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>5009868.646</t>
+          <t>-2.94448909698986e-11</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-238287.253</t>
+          <t>-3.60955709766131e-11</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>-260091.912</t>
+          <t>3.91615628814179e-11</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-271245.199</t>
+          <t>-5.8250293477613e-11</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-292851.937</t>
+          <t>8.98836560736527e-11</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-309693.079</t>
+          <t>3.83124643121846e-11</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-344900.639</t>
+          <t>3.8340886021615e-11</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>-356106.299</t>
+          <t>1.04023456515279e-10</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>-320702.298</t>
+          <t>-3.00701685773674e-11</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-303323.388</t>
+          <t>1.72803993336856e-11</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>-237536.435</t>
+          <t>-4.20072865381371e-11</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>-245126.246</t>
+          <t>-5.3887561080046e-11</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>-114754.022</t>
+          <t>-1.87583282240666e-11</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>14445.24</t>
+          <t>1.77919901034329e-11</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>-11089.385</t>
+          <t>2.97148972094874e-11</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>87505.678</t>
+          <t>8.28492829896277e-11</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>237549.724</t>
+          <t>-4.0870418160921e-11</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>75934.396</t>
+          <t>-1.95086613530293e-10</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>123918.924</t>
+          <t>1.36765265779104e-10</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>3413000.044</t>
+          <t>-3.95630195271224e-11</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>3411071.673</t>
+          <t>3.07522896036971e-11</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>3741968.382</t>
+          <t>-1.3579892765847e-10</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>3688627.404</t>
+          <t>1.18404841487063e-10</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>3850459.319</t>
+          <t>1.15960574476048e-11</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>3910300.898</t>
+          <t>-9.46442924032453e-11</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>4227335.057</t>
+          <t>1.31251454149606e-10</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>4354920.835</t>
+          <t>3.2855496101547e-11</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>13371315.302</t>
+          <t>5.66840171813965e-05</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>7048597.791</t>
+          <t>-1.91330909729004e-05</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>7213604.041</t>
+          <t>-3.57627868652344e-06</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>6983308.039</t>
+          <t>-2.20537185668945e-06</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>7246429.582</t>
+          <t>2.36630439758301e-05</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>7362871.449</t>
+          <t>8.94069671630859e-07</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>7513822.627</t>
+          <t>3.14116477966309e-05</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>7586732.398</t>
+          <t>4.21404838562012e-05</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>7733109.323</t>
+          <t>2.16960906982422e-05</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>8152864.014</t>
+          <t>-1.29342079162598e-05</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>8388495.251</t>
+          <t>2.6404857635498e-05</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>8499204.214</t>
+          <t>-3.45110893249512e-05</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>8580476.522</t>
+          <t>-1.15633010864258e-05</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>8752068.03</t>
+          <t>2.63452529907227e-05</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>8564257.246</t>
+          <t>3.04579734802246e-05</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>8720151.215</t>
+          <t>2.65836715698242e-05</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>9004245.147</t>
+          <t>-2.1815299987793e-05</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>9012906.613</t>
+          <t>-3.36170196533203e-05</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>9212239.792</t>
+          <t>8.76188278198242e-06</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>9216113.71</t>
+          <t>2.86102294921875e-05</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>9342523.661</t>
+          <t>2.11596488952637e-05</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>10410264.821</t>
+          <t>6.31213188171387e-05</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>10379847.159</t>
+          <t>3.01003456115723e-05</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10973562.471</t>
+          <t>2.45571136474609e-05</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>11096733.118</t>
+          <t>-1.31130218505859e-06</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12014640.696</t>
+          <t>2.38418579101562e-06</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>12602599.047</t>
+          <t>2.0444393157959e-05</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>43.349</t>
+          <t>10106124.3879674</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>45.677</t>
+          <t>10465838.2685081</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>51.181</t>
+          <t>11158150.4147994</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>51.473</t>
+          <t>11493028.3387952</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>56.414</t>
+          <t>12558675.3259967</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>68.559</t>
+          <t>14710494.1069129</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>70.325</t>
+          <t>15353158.4285828</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>68.945</t>
+          <t>14901314.7468654</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>64.708</t>
+          <t>13214737.479765</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>66.874</t>
+          <t>13975270.8287043</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>73.555</t>
+          <t>14685076.2360245</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>79.902</t>
+          <t>16349559.8553165</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>83.248</t>
+          <t>16833959.2810382</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>86.083</t>
+          <t>17290967.7819541</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>83.853</t>
+          <t>17644332.3463888</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>98.291</t>
+          <t>20299939.5365793</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>105.781</t>
+          <t>21268104.0432005</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>116.846</t>
+          <t>24169838.4070811</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>116.108</t>
+          <t>23355114.1029043</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>119.319</t>
+          <t>23693674.5369712</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>135.06</t>
+          <t>27741368.5440909</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>136.589</t>
+          <t>27846419.7232516</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>142.874</t>
+          <t>29187525.0858074</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>146.798</t>
+          <t>29818078.9302808</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>157.028</t>
+          <t>31800713.9287628</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>161.948</t>
+          <t>32727394.2901374</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>166.699</t>
+          <t>34003633.8313107</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>8050307.111</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>4047495.086</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>4109001.932</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>4150720.755</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>4201220.71</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>4264966.243</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>4299019.827</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>4349119.533</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>4395374.009</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>4429418.709</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>4497459.042</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>4552546.417</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>4621118.608</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>4670881.471</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>4624773.044</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>4650440.744</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>4735438.675</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>4746116.736</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>4850256.253</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>4886221.843</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>4935592.646</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>5555449.259</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>5546189.228</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>5862121.252</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>5925058.06</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>6440999.348</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>6704218.937</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>26.098</t>
+          <t>16402957.1369738</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>26.229</t>
+          <t>17071159.6397211</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>29.154</t>
+          <t>18893014.4522787</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>30.594</t>
+          <t>19468101.9274015</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>32.707</t>
+          <t>21398439.910887</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>39.713</t>
+          <t>25544137.5235769</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>40.237</t>
+          <t>26338545.9681022</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>39.523</t>
+          <t>25651516.5836977</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>36.779</t>
+          <t>23494153.6235755</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>36.332</t>
+          <t>23617253.4230231</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>39.436</t>
+          <t>25173611.5038354</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>42.799</t>
+          <t>27179641.7627194</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>44.834</t>
+          <t>27552940.6342802</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>45.941</t>
+          <t>28015829.5199088</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>45.281</t>
+          <t>28873203.4289683</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>52.418</t>
+          <t>32474939.5598421</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>55.632</t>
+          <t>34182684.025373</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>61.53</t>
+          <t>38174578.6055611</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>61.131</t>
+          <t>37393920.4434314</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>63.261</t>
+          <t>38229805.9432173</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>71.351</t>
+          <t>44145415.2624007</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>72.891</t>
+          <t>44800424.9596128</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>76.341</t>
+          <t>46963148.1094301</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>78.42</t>
+          <t>47375833.9038918</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>83.845</t>
+          <t>50445053.9151983</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>86.82</t>
+          <t>51943331.6246279</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>88.679</t>
+          <t>54302403.9183497</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>3810300.076</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>1841006.086</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>2086898.006</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2494261.681</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>2284553.824</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>2412279.666</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2496897.875</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>2605498.643</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>2623430.614</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>2452051.842</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>2449584.194</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>2629834.569</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>2589175.461</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>2598282.587</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>2670070.835</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>2544246.391</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>2572328.406</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>2550336.397</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>2520050.348</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>2426111.61</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>2345239.213</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>2818196.764</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>2685358.198</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>2978292.892</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>2761469.432</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>3269955.792</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>3399924.573</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>31.48</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>-112.94</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>-112.46</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>-110.87</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>-112.82</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>-112.84</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>-113.81</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>-113.67</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>-112.22</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>-112.37</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>-109.7</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>-109.32</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>-104.43</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>-99.44</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>-100.42</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>-96.56</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>-90.77</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>-97.02</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>-95.08</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>40.68</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>45.45</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>32.78</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>37.36</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>29.28</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>41.6</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>29.28</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>28.09</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>22634988.814</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>30953695.241</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>28555.158</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>5053.451</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>5934.263</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>20730.492</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>422862.899</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>2174.67</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>32538.436</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>2446.52</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>30051.795</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>3329.483</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>205397.018</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>68854.518</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>13088.001</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>1453.02</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>78676.915</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>1266.077</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>849.286</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>40149978.512</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>4553651202.698</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>10246478.839</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>-2590669942.005</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>3493029.498</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>3274108.926</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>3561627.885</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>3647297.304</t>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>10946712.9457346</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>11783020.926745</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>13199002.7197885</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>13087370.0365618</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>14138844.5672582</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>16737418.8918727</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>16937528.9416037</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>17136929.1747667</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>16346831.0730468</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>16977535.231846</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>18608818.240082</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>19747598.4660867</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>20761159.4761772</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>20968208.3362979</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>20328806.7612598</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>24239864.530799</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>25753106.8485841</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>28044926.9519072</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>28514625.2711745</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>29376482.1646107</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>32667976.879407</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>33653611.6304402</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>34275115.8692785</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>35302282.0791542</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>38451923.3356889</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>39610471.6868776</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>39577225.9550582</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>5009868645972.94</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>-238287252800.557</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>-260091912080.894</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>-271245198680.244</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-292851936639.706</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-309693078729.713</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>-344900638873.668</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>-356106298675.43</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>-320702297735.847</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>-303323387956.723</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>-237536434818.011</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>-245126245998.903</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>-114754021723.543</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>14445240080.8567</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>-11089385110.1073</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>87505677670.2445</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>237549724464.341</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>75934396148.1952</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>123918924486.318</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>3413000043815.6</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>3411071672859.09</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>3741968381816.08</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>3688627404384.96</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>3850459318990.41</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>3910300898135.68</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>4227335057237.89</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>4354920835403</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>11000657388748.8</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>5232651458400.1</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>5333773701840.16</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>5386235290359.54</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>5459557684239.9</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>5554913631320.39</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>5631652779612.69</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>5709485456839.75</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>5783239120360.65</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>5840760727280.46</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>5963892532439.7</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>6091927764000.48</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>6206653288239.95</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>6339773926320.28</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>6312404541799.85</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>6321974889040.39</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>6493726573759.86</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>6537703841800.28</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>6647957989080.08</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>6678508400355.47</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>6782760548942.46</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>7654694295913.99</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>7630963815666.89</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>8072181981344.58</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>8128137498352.54</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>8827988904486.81</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>9176606757764.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>8050307111481.52</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>4047495086127.72</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>4109001931640.88</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>4150720755378.24</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>4201220709579.23</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>4264966243075.6</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>4299019827271.16</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>4349119532746.19</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>4395374009420.79</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>4429418709391.17</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>4497459042005.93</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>4552546416667.94</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>4621118608214.69</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>4670881471206.42</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>4624773044027.57</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>4650440744015.68</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>4735438674901.98</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>4746116735810.5</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>4850256252732.54</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>4886221843155.83</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>4935592646444.66</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>5555449259346.76</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>5546189228144.11</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>5862121252276.54</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>5925058059746.98</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>6440999347850.1</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>6704218936548.77</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>5030830622.12558</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2421184553.00005</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2460120922.00008</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2481972520.00021</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2525222686.00019</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2569599396.99984</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2602571446.00022</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2643028113</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2683428103.99983</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>2709457044.00017</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2765362170.99963</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>2796728309.99991</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>2862591956.99984</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>2945442663.00011</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>2944472079.00002</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>2965027470.00019</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>3024664026.00034</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>3042368246.99991</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>3104552511.99989</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>3114105934.70157</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>3152193813.76175</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>3546101709.8212</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>3531887168.07331</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>3730031407.21429</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>3746112812.75699</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>4065731583.40256</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>4221800255.62903</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2397237689.94836</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1010922944.0441</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1199235409.84141</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1210630433.00015</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1198223382.08405</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>1249011334.99981</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1262331377.00031</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>1282979381.0003</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>1307228483.99982</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>1325152161.00007</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>1365398164.99947</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>1380874830.99982</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>1433557617.99937</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>1491668234.00004</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>1485383547.00007</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>1516618618.00037</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>1576852067.00007</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>1549631194.99977</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>1594721801.00009</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>1617765845.78776</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>1623330653.70467</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>1793076630.9851</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>1768500917.40007</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>1846455785.00133</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>1870705973.81567</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>2023138495.80353</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>2086420813.30221</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>11000657388748.8</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>5232651458400.1</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>5333773701840.16</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>5386235290359.54</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>5459557684239.9</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>5554913631320.39</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>5631652779612.69</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>5709485456839.75</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>5783239120360.65</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>5840760727280.46</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>5963892532439.7</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>6091927764000.48</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>6206653288239.95</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>6339773926320.28</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>6312404541799.85</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>6321974889040.39</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>6493726573759.86</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>6537703841800.28</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>6647957989080.08</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>6678508400355.47</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>6782760548942.46</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>7654694295913.99</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>7630963815666.89</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>8072181981344.58</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>8128137498352.54</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>8827988904486.81</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>9176606757764.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>5009868645972.94</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>-238287252800.557</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>-260091912080.894</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>-271245198680.244</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-292851936639.706</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>-309693078729.713</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>-344900638873.668</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>-356106298675.43</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>-320702297735.847</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>-303323387956.723</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>-237536434818.011</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>-245126245998.903</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>-114754021723.543</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>14445240080.8567</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>-11089385110.1073</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>87505677670.2445</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>237549724464.341</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>75934396148.1952</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>123918924486.318</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>3413000043815.6</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>3411071672859.09</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>3741968381816.08</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>3688627404384.96</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>3850459318990.41</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>3910300898135.68</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>4227335057237.89</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>4354920835403</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>54350274.2827501</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>57209883.8151937</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>64271647.1876827</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>64622574.1065296</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>71023838.1844459</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>86657240.0827002</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>88750773.4552537</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>86847033.7418469</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>81173223.2938115</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>83709594.9808901</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>92103355.3348949</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>99948801.7679264</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>103975761.651795</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>107515443.752738</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>105157924.510046</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>123532765.103892</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>133083978.216761</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>147268078.882938</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>146363425.745529</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>150601270.332599</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>171285779.629825</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>173305227.25441</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>181224134.969356</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>186509735.397727</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>199761577.622657</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>206167238.989671</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>212326779.862302</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>18839927.3381845</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>19515870.3478496</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>21781207.5677877</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>22088209.8223135</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>24402627.602647</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>29247109.553696</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>30184421.5317737</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>29176901.6484656</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>26887461.4385939</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>27178762.915221</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>29207197.2599662</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>31539321.4309894</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>32077764.3699587</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>32949290.5486919</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>33815395.5954899</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>38259761.0834794</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>40423380.5953364</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>45365957.5714653</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>44457564.1180814</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>45519658.9228999</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>52536884.9528768</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>53180878.5887684</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>56228974.5039241</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>56741301.8515121</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>60297915.1357863</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>61927728.3661537</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>64906356.4569697</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
         </is>
       </c>
     </row>
@@ -3614,7 +5855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3637,36 +5878,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3678,331 +5934,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -4039,6 +6659,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
